--- a/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="514">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T08:56:46+00:00</t>
+    <t>2026-07-14T09:07:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -849,13 +849,16 @@
 </t>
   </si>
   <si>
+    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization). Keine Verwendung im Medikationsplan.</t>
+  </si>
+  <si>
     <t>MedicationRequest.reported[x]:reportedBoolean</t>
   </si>
   <si>
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>Quelle der Information. Mögliche Ausprägungen: [ true | false ]. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
+    <t>Quelle der Information. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -4845,7 +4848,7 @@
         <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>255</v>
@@ -4931,13 +4934,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>253</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>21</v>
@@ -4962,7 +4965,7 @@
         <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>255</v>
@@ -5048,10 +5051,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5074,16 +5077,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5133,7 +5136,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5148,27 +5151,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5191,16 +5194,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5250,7 +5253,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>90</v>
@@ -5265,27 +5268,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5308,16 +5311,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5367,7 +5370,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5382,27 +5385,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>179</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5425,13 +5428,13 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5482,7 +5485,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5497,16 +5500,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5514,10 +5517,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5540,13 +5543,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5597,7 +5600,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5612,27 +5615,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5655,13 +5658,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5712,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5727,16 +5730,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5744,10 +5747,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5770,13 +5773,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5827,7 +5830,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5842,16 +5845,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5888,13 +5891,13 @@
         <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5923,10 +5926,10 @@
         <v>187</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5944,7 +5947,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5959,13 +5962,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5976,10 +5979,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6002,13 +6005,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6059,7 +6062,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6080,10 +6083,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6091,10 +6094,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6120,13 +6123,13 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6155,10 +6158,10 @@
         <v>187</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6176,7 +6179,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6191,27 +6194,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6234,16 +6237,16 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6293,7 +6296,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6308,16 +6311,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>179</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6325,10 +6328,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6351,13 +6354,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6408,7 +6411,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6423,13 +6426,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6440,10 +6443,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6469,10 +6472,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6523,7 +6526,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6544,7 +6547,7 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6555,10 +6558,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6581,13 +6584,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6638,7 +6641,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6653,13 +6656,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6670,10 +6673,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6699,14 +6702,14 @@
         <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6755,7 +6758,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6770,13 +6773,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6787,10 +6790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6816,13 +6819,13 @@
         <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6851,10 +6854,10 @@
         <v>187</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6872,7 +6875,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6896,7 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6904,10 +6907,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6930,13 +6933,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6987,7 +6990,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7002,13 +7005,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7019,10 +7022,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7045,13 +7048,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7102,7 +7105,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7117,13 +7120,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7134,10 +7137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7160,16 +7163,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7219,7 +7222,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7234,13 +7237,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7251,10 +7254,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7277,13 +7280,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7334,7 +7337,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7352,10 +7355,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7366,10 +7369,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7481,10 +7484,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7598,14 +7601,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7627,10 +7630,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>159</v>
@@ -7685,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7717,10 +7720,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7743,16 +7746,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7802,7 +7805,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7823,7 +7826,7 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7834,10 +7837,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7949,10 +7952,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8066,14 +8069,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8095,10 +8098,10 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>159</v>
@@ -8153,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8185,10 +8188,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8211,13 +8214,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8268,7 +8271,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8289,7 +8292,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8300,10 +8303,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8326,13 +8329,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8383,7 +8386,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8404,7 +8407,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8415,10 +8418,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8441,13 +8444,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8498,7 +8501,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8519,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8530,10 +8533,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8556,19 +8559,19 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8617,7 +8620,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8635,10 +8638,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8649,10 +8652,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8675,16 +8678,16 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8734,7 +8737,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8752,24 +8755,24 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8792,13 +8795,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8849,7 +8852,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8867,24 +8870,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8907,16 +8910,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8966,7 +8969,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8984,10 +8987,10 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8998,10 +9001,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9024,13 +9027,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9081,7 +9084,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9102,10 +9105,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9113,10 +9116,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9139,13 +9142,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9196,7 +9199,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9214,10 +9217,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9228,10 +9231,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9343,10 +9346,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9460,14 +9463,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9489,10 +9492,10 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>159</v>
@@ -9547,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9579,10 +9582,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9605,16 +9608,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9643,10 +9646,10 @@
         <v>187</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9664,7 +9667,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -9682,24 +9685,24 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9725,10 +9728,10 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9758,10 +9761,10 @@
         <v>187</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9779,7 +9782,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9797,24 +9800,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9837,13 +9840,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9894,7 +9897,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9909,13 +9912,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9926,14 +9929,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9952,16 +9955,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10011,7 +10014,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10032,7 +10035,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10043,10 +10046,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10069,16 +10072,16 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10128,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10143,13 +10146,13 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:07:25+00:00</t>
+    <t>2026-07-16T16:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
